--- a/artfynd/A 59111-2021 artfynd.xlsx
+++ b/artfynd/A 59111-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 59111-2021 artfynd.xlsx
+++ b/artfynd/A 59111-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>79652482</v>
+        <v>79652427</v>
       </c>
       <c r="B2" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lille Mölebo, 550 m N, Sm</t>
+          <t>Lilla Mölebo, 500 m NNV, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562087.4819995024</v>
+        <v>561965</v>
       </c>
       <c r="R2" t="n">
-        <v>6284921.353342758</v>
+        <v>6284726</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,19 +754,9 @@
           <t>2019-08-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-08-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,6 +768,26 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Stående död gran.</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående död gran.</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -791,15 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>79652565</v>
+        <v>79652482</v>
       </c>
       <c r="B3" t="n">
-        <v>88921</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +815,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5741</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -830,14 +838,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lilla Mölebo, 550 m NNV, Sm</t>
+          <t>Lille Mölebo, 550 m N, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561976.3460291948</v>
+        <v>562087</v>
       </c>
       <c r="R3" t="n">
-        <v>6284810.45812476</v>
+        <v>6284921</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,19 +875,9 @@
           <t>2019-08-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-08-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>79652427</v>
+        <v>79652564</v>
       </c>
       <c r="B4" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,45 +916,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1339</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lilla Mölebo, 500 m NNV, Sm</t>
+          <t>Lilla Mölebo, 550 m NNV, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561964.9438661111</v>
+        <v>561976</v>
       </c>
       <c r="R4" t="n">
-        <v>6284725.740683257</v>
+        <v>6284810</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -991,19 +976,9 @@
           <t>2019-08-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-08-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,26 +990,6 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>Stående död gran.</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående död gran.</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1051,37 +1006,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>79652564</v>
+        <v>79652565</v>
       </c>
       <c r="B5" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91409</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5420</v>
+        <v>5741</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1094,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561976.3460291948</v>
+        <v>561976</v>
       </c>
       <c r="R5" t="n">
-        <v>6284810.45812476</v>
+        <v>6284810</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1127,19 +1077,9 @@
           <t>2019-08-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-08-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 59111-2021 artfynd.xlsx
+++ b/artfynd/A 59111-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -801,6 +806,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79652427</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79652482</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79652564</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,8 +1124,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79652565</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>